--- a/data/trans_dic/IP31KM11_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM11_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>96,8; 100,0</t>
+          <t>91,6; 98,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>75,35; 97,13</t>
+          <t>96,73; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,5; 98,21</t>
+          <t>95,04; 98,78</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>97,2; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>97,93; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98,76; 100,0</t>
+          <t>98,93; 100,0</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>94,71%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>94,11%</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>85,55; 98,8</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>83,54; 98,81</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90,32; 99,32</t>
+          <t>91,6; 99,37</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>97,19; 100,0</t>
+          <t>95,11; 99,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>95,58; 99,46</t>
+          <t>96,81; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97,37; 99,48</t>
+          <t>96,83; 99,29</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>94,46; 99,38</t>
+          <t>93,35; 99,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>95,29; 99,41</t>
+          <t>94,06; 99,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96,18; 99,16</t>
+          <t>95,18; 98,96</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93,12; 99,27</t>
+          <t>92,33; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93,78; 99,77</t>
+          <t>92,18; 99,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95,33; 99,41</t>
+          <t>94,79; 99,24</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>98,08; 99,48</t>
+          <t>96,15; 98,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>94,53; 98,22</t>
+          <t>97,95; 99,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96,33; 98,63</t>
+          <t>97,29; 98,73</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>151</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>101041</t>
+          <t>116280</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>124787</t>
+          <t>99715</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225829</t>
+          <t>215995</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98454; 101709</t>
+          <t>111030; 119008</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>101859; 131300</t>
+          <t>97072; 100349</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>204904; 232656</t>
+          <t>210572; 218850</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>137</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>92931</t>
+          <t>89880</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95028</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>186640</t>
+          <t>184908</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90776; 93392</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>93434; 95410</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>184779; 187101</t>
+          <t>183312; 185290</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50089</t>
+          <t>52891</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58665</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>108753</t>
+          <t>104901</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>47774; 55172</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>52072; 61590</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>101544; 111653</t>
+          <t>98792; 107174</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>269</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>213954</t>
+          <t>193317</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>208797</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>422752</t>
+          <t>368226</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>209479; 215537</t>
+          <t>187670; 195910</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>203249; 211501</t>
+          <t>171000; 176640</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>416950; 425985</t>
+          <t>362111; 371291</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>167</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>113092</t>
+          <t>142095</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>156465</t>
+          <t>112924</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>269557</t>
+          <t>255019</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>109114; 114796</t>
+          <t>135903; 144684</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>151953; 158520</t>
+          <t>108603; 114822</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>264464; 272671</t>
+          <t>248468; 258328</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>96</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>67152</t>
+          <t>64494</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>68058</t>
+          <t>68514</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>135209</t>
+          <t>133008</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>64154; 68394</t>
+          <t>60810; 65863</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>64738; 68876</t>
+          <t>64855; 69880</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>131485; 137117</t>
+          <t>129129; 135192</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>891</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>901</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>638259</t>
+          <t>658957</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>710480</t>
+          <t>603101</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1348739</t>
+          <t>1262058</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>632719; 641765</t>
+          <t>649676; 665197</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>692275; 719317</t>
+          <t>597723; 606585</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1326911; 1358627</t>
+          <t>1251034; 1269575</t>
         </is>
       </c>
     </row>
